--- a/ig/DM-JUILLET-2025/ValueSet-JDV-J164-GlucoseNumberOfDays-ENS.xlsx
+++ b/ig/DM-JUILLET-2025/ValueSet-JDV-J164-GlucoseNumberOfDays-ENS.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20241213120000</t>
+    <t>20250728120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -99,31 +99,31 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>GEN-275</t>
+    <t>#GEN-275</t>
   </si>
   <si>
     <t>7j</t>
   </si>
   <si>
-    <t>GEN-276</t>
+    <t>#GEN-276</t>
   </si>
   <si>
     <t>14j</t>
   </si>
   <si>
-    <t>GEN-277</t>
+    <t>#GEN-277</t>
   </si>
   <si>
     <t>30j</t>
   </si>
   <si>
-    <t>GEN-278</t>
+    <t>#GEN-278</t>
   </si>
   <si>
     <t>90j</t>
   </si>
   <si>
-    <t>GEN-092.08.05</t>
+    <t>#GEN-092.08.05</t>
   </si>
   <si>
     <t>Autre(s) nombre de jours</t>
@@ -135,7 +135,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/1.2.250.1.213.1.1.4.322</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis</t>
   </si>
 </sst>
 </file>
